--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4806" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4806" uniqueCount="690">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -729,7 +729,7 @@
     <t>Practitioner.identifier.use</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>The purpose of this identifier.</t>
@@ -1089,9 +1089,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.type</t>
@@ -8937,7 +8934,7 @@
         <v>164</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>347</v>
+        <v>229</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>230</v>
@@ -9024,7 +9021,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>238</v>
@@ -9140,7 +9137,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>249</v>
@@ -9169,7 +9166,7 @@
         <v>130</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>251</v>
@@ -9185,7 +9182,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>21</v>
@@ -9256,7 +9253,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>261</v>
@@ -9370,7 +9367,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>271</v>
@@ -9482,7 +9479,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>280</v>
@@ -9596,7 +9593,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>290</v>
@@ -9708,7 +9705,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>292</v>
@@ -9822,7 +9819,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>294</v>
@@ -9936,7 +9933,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>301</v>
@@ -10050,7 +10047,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>309</v>
@@ -10164,7 +10161,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>316</v>
@@ -10207,7 +10204,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>21</v>
@@ -10278,10 +10275,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10304,26 +10301,26 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="O69" t="s" s="2">
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="P69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q69" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="R69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10367,7 +10364,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10385,21 +10382,21 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>370</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10422,19 +10419,19 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10483,7 +10480,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10498,13 +10495,13 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AM70" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -10512,10 +10509,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10624,10 +10621,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10738,10 +10735,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10767,16 +10764,16 @@
         <v>164</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10804,28 +10801,28 @@
         <v>185</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z73" t="s" s="2">
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10840,13 +10837,13 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AM73" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10854,10 +10851,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10883,16 +10880,16 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10941,7 +10938,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10956,10 +10953,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
@@ -10970,14 +10967,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10999,13 +10996,13 @@
         <v>102</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11055,7 +11052,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11070,13 +11067,13 @@
         <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -11084,14 +11081,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11113,13 +11110,13 @@
         <v>102</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11169,7 +11166,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11184,13 +11181,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11198,10 +11195,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11227,10 +11224,10 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11281,7 +11278,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11296,13 +11293,13 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL77" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AM77" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11310,10 +11307,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11339,10 +11336,10 @@
         <v>102</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11393,7 +11390,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11408,10 +11405,10 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
@@ -11422,10 +11419,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11451,14 +11448,14 @@
         <v>272</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11507,7 +11504,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11522,10 +11519,10 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL79" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>278</v>
@@ -11536,10 +11533,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11562,19 +11559,19 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11623,7 +11620,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11638,13 +11635,13 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AL80" t="s" s="2">
+      <c r="AM80" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11652,10 +11649,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11678,19 +11675,19 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11739,7 +11736,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11754,13 +11751,13 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AM81" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -11768,10 +11765,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11880,10 +11877,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11994,13 +11991,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>21</v>
@@ -12022,13 +12019,13 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12108,10 +12105,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12137,16 +12134,16 @@
         <v>164</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12159,7 +12156,7 @@
         <v>21</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>21</v>
@@ -12174,28 +12171,28 @@
         <v>185</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12210,13 +12207,13 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12224,10 +12221,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12253,13 +12250,13 @@
         <v>164</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12273,7 +12270,7 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>21</v>
@@ -12288,28 +12285,28 @@
         <v>185</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="Z86" t="s" s="2">
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12324,10 +12321,10 @@
         <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -12338,10 +12335,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12367,16 +12364,16 @@
         <v>102</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="N87" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="O87" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -12389,43 +12386,43 @@
         <v>21</v>
       </c>
       <c r="T87" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12440,10 +12437,10 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
@@ -12454,10 +12451,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12483,10 +12480,10 @@
         <v>102</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12501,43 +12498,43 @@
         <v>21</v>
       </c>
       <c r="T88" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12552,13 +12549,13 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AL88" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AL88" t="s" s="2">
+      <c r="AM88" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
@@ -12566,10 +12563,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12595,10 +12592,10 @@
         <v>102</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12678,10 +12675,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12707,7 +12704,7 @@
         <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>209</v>
@@ -12788,13 +12785,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C91" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>21</v>
@@ -12816,13 +12813,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12891,7 +12888,7 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>21</v>
@@ -12902,10 +12899,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13014,10 +13011,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13043,7 +13040,7 @@
         <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>209</v>
@@ -13126,10 +13123,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13155,13 +13152,13 @@
         <v>130</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13169,49 +13166,49 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>88</v>
@@ -13240,10 +13237,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13269,10 +13266,10 @@
         <v>102</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13323,7 +13320,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13352,13 +13349,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>21</v>
@@ -13380,13 +13377,13 @@
         <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13455,7 +13452,7 @@
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
@@ -13466,10 +13463,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13578,10 +13575,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13607,7 +13604,7 @@
         <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>209</v>
@@ -13690,10 +13687,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13719,13 +13716,13 @@
         <v>130</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13733,7 +13730,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>21</v>
@@ -13775,7 +13772,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>88</v>
@@ -13804,10 +13801,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13833,10 +13830,10 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13887,7 +13884,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13916,13 +13913,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>21</v>
@@ -13944,13 +13941,13 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14019,7 +14016,7 @@
         <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>21</v>
@@ -14030,10 +14027,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14142,10 +14139,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14171,7 +14168,7 @@
         <v>109</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>209</v>
@@ -14254,10 +14251,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14283,13 +14280,13 @@
         <v>130</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14297,7 +14294,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>21</v>
@@ -14339,7 +14336,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>88</v>
@@ -14368,10 +14365,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14397,10 +14394,10 @@
         <v>102</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14451,7 +14448,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14480,13 +14477,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C106" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>21</v>
@@ -14508,13 +14505,13 @@
         <v>21</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14574,7 +14571,7 @@
         <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>117</v>
@@ -14594,10 +14591,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14706,10 +14703,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14735,7 +14732,7 @@
         <v>109</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>209</v>
@@ -14818,10 +14815,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14847,13 +14844,13 @@
         <v>130</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14861,7 +14858,7 @@
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>21</v>
@@ -14903,7 +14900,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>88</v>
@@ -14932,10 +14929,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14961,10 +14958,10 @@
         <v>102</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15015,7 +15012,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15044,10 +15041,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15073,10 +15070,10 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15100,34 +15097,34 @@
         <v>21</v>
       </c>
       <c r="W111" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF111" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15156,14 +15153,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15185,10 +15182,10 @@
         <v>102</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15203,43 +15200,43 @@
         <v>21</v>
       </c>
       <c r="T112" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15254,13 +15251,13 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AL112" t="s" s="2">
+      <c r="AM112" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>21</v>
@@ -15268,14 +15265,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15297,13 +15294,13 @@
         <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15317,43 +15314,43 @@
         <v>21</v>
       </c>
       <c r="T113" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15368,10 +15365,10 @@
         <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AL113" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>21</v>
@@ -15382,14 +15379,14 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15411,10 +15408,10 @@
         <v>102</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15465,7 +15462,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15480,13 +15477,13 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL114" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AL114" t="s" s="2">
+      <c r="AM114" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
@@ -15494,14 +15491,14 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15523,10 +15520,10 @@
         <v>102</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15541,43 +15538,43 @@
         <v>21</v>
       </c>
       <c r="T115" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF115" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15592,13 +15589,13 @@
         <v>100</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AL115" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AL115" t="s" s="2">
+      <c r="AM115" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -15606,10 +15603,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15635,13 +15632,13 @@
         <v>102</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15691,7 +15688,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15706,13 +15703,13 @@
         <v>100</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="AL116" t="s" s="2">
+      <c r="AM116" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -15720,10 +15717,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15749,14 +15746,14 @@
         <v>272</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -15769,43 +15766,43 @@
         <v>21</v>
       </c>
       <c r="T117" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF117" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15820,10 +15817,10 @@
         <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>278</v>
@@ -15834,10 +15831,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15863,14 +15860,14 @@
         <v>164</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -15898,11 +15895,11 @@
         <v>185</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z118" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="Z118" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="AA118" t="s" s="2">
         <v>21</v>
       </c>
@@ -15919,7 +15916,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15934,13 +15931,13 @@
         <v>100</v>
       </c>
       <c r="AK118" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AL118" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="AL118" t="s" s="2">
+      <c r="AM118" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>21</v>
@@ -15948,10 +15945,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15977,10 +15974,10 @@
         <v>102</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16060,10 +16057,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16089,7 +16086,7 @@
         <v>109</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M120" t="s" s="2">
         <v>209</v>
@@ -16170,13 +16167,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C121" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>21</v>
@@ -16198,13 +16195,13 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16264,7 +16261,7 @@
         <v>79</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>117</v>
@@ -16284,10 +16281,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16313,10 +16310,10 @@
         <v>102</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16367,7 +16364,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16396,10 +16393,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16422,17 +16419,17 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -16481,7 +16478,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16496,13 +16493,13 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL123" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AL123" t="s" s="2">
+      <c r="AM123" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
@@ -16510,10 +16507,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16536,17 +16533,17 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>21</v>
@@ -16595,7 +16592,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16613,10 +16610,10 @@
         <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AM124" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>21</v>
@@ -16624,10 +16621,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16650,13 +16647,13 @@
         <v>21</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16707,7 +16704,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16722,13 +16719,13 @@
         <v>100</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>21</v>
@@ -16736,10 +16733,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16848,10 +16845,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16962,14 +16959,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16991,16 +16988,16 @@
         <v>109</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -17049,7 +17046,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17078,10 +17075,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17107,14 +17104,14 @@
         <v>212</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -17163,7 +17160,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17181,7 +17178,7 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>21</v>
@@ -17192,10 +17189,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17221,10 +17218,10 @@
         <v>239</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17254,11 +17251,11 @@
         <v>154</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="Z130" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="Z130" t="s" s="2">
-        <v>671</v>
-      </c>
       <c r="AA130" t="s" s="2">
         <v>21</v>
       </c>
@@ -17275,7 +17272,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>88</v>
@@ -17293,10 +17290,10 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
@@ -17304,10 +17301,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17333,14 +17330,14 @@
         <v>272</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>21</v>
@@ -17389,7 +17386,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17407,10 +17404,10 @@
         <v>21</v>
       </c>
       <c r="AL131" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AM131" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>21</v>
@@ -17418,10 +17415,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17447,10 +17444,10 @@
         <v>281</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17501,7 +17498,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17519,7 +17516,7 @@
         <v>21</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>21</v>
@@ -17530,10 +17527,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17559,16 +17556,16 @@
         <v>239</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>21</v>
@@ -17617,7 +17614,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17632,13 +17629,13 @@
         <v>100</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="AM133" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
